--- a/fulls/full_mestre_lf2a_2026.xlsx
+++ b/fulls/full_mestre_lf2a_2026.xlsx
@@ -35042,41 +35042,41 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>A. BOBAR</t>
+          <t>S. LLANOS GASULLA</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H21" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" s="8" t="n">
         <v>-2</v>
       </c>
       <c r="K21" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L21" s="9" t="n">
         <v>0.8621</v>
@@ -35085,7 +35085,7 @@
         <v>1.1733</v>
       </c>
       <c r="N21" s="10" t="n">
-        <v>0.0784</v>
+        <v>0.1567</v>
       </c>
     </row>
     <row r="22">
@@ -35096,18 +35096,18 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>S. LLANOS GASULLA</t>
+          <t>A. IVAN</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -35121,16 +35121,16 @@
         </is>
       </c>
       <c r="H22" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J22" s="8" t="n">
         <v>-2</v>
       </c>
       <c r="K22" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
         <v>0.8621</v>
@@ -35139,7 +35139,7 @@
         <v>1.1733</v>
       </c>
       <c r="N22" s="10" t="n">
-        <v>0.1567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -35150,7 +35150,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>A. IVAN</t>
+          <t>A. BOBAR</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
@@ -35161,12 +35161,12 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -35175,7 +35175,7 @@
         </is>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="8" t="n">
         <v>0</v>
@@ -35193,7 +35193,7 @@
         <v>1.1733</v>
       </c>
       <c r="N23" s="10" t="n">
-        <v>0</v>
+        <v>0.0784</v>
       </c>
     </row>
     <row r="24">
@@ -35204,18 +35204,18 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>N. MARTÍNEZ MARTÍNEZ</t>
+          <t>E. CASTRO LUTZARDO</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -35225,7 +35225,7 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H24" s="8" t="n">
@@ -35258,28 +35258,28 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>S. TORRUELLA BRETÓN</t>
+          <t>N. MARTÍNEZ MARTÍNEZ</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H25" s="8" t="n">
@@ -35292,7 +35292,7 @@
         <v>2</v>
       </c>
       <c r="K25" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
         <v>1.1733</v>
@@ -35312,14 +35312,14 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>E. CASTRO LUTZARDO</t>
+          <t>S. TORRUELLA BRETÓN</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
@@ -35328,12 +35328,12 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H26" s="8" t="n">
@@ -35346,7 +35346,7 @@
         <v>2</v>
       </c>
       <c r="K26" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L26" s="9" t="n">
         <v>1.1733</v>
@@ -35474,41 +35474,41 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>P. DE MIER ESPINA</t>
+          <t>N. IPO SERICHE-DOUGAN</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H29" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L29" s="9" t="n">
         <v>1.8895</v>
@@ -35517,7 +35517,7 @@
         <v>0.6</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>0</v>
+        <v>0.1453</v>
       </c>
     </row>
     <row r="30">
@@ -35582,41 +35582,41 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>N. IPO SERICHE-DOUGAN</t>
+          <t>P. DE MIER ESPINA</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
       <c r="H31" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L31" s="9" t="n">
         <v>1.8895</v>
@@ -35625,7 +35625,7 @@
         <v>0.6</v>
       </c>
       <c r="N31" s="10" t="n">
-        <v>0.1453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -36284,7 +36284,7 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>C. UGOCHUKWU UGOCHUKWU</t>
+          <t>E. FLOREZ PASCUAL</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
@@ -36392,7 +36392,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>E. FLOREZ PASCUAL</t>
+          <t>C. UGOCHUKWU UGOCHUKWU</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
@@ -36446,7 +36446,7 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>N. GOMEZ COBO</t>
+          <t>M. GOMEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
@@ -36474,7 +36474,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" s="8" t="n">
         <v>3</v>
@@ -36554,7 +36554,7 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>M. GOMEZ HERNANDEZ</t>
+          <t>E. ABUBAKAR ARREY</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
@@ -36582,7 +36582,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" s="8" t="n">
         <v>3</v>
@@ -36608,7 +36608,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>E. ABUBAKAR ARREY</t>
+          <t>N. GOMEZ COBO</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
@@ -36932,7 +36932,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>M. ANGULO QUINTANA</t>
+          <t>L. TESSON</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
@@ -36986,14 +36986,14 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>L. TESSON</t>
+          <t>C. LOUREIRO CURRAS</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
@@ -37002,12 +37002,12 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">
@@ -37040,14 +37040,14 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>C. LOUREIRO CURRAS</t>
+          <t>M. ANGULO QUINTANA</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
@@ -37056,12 +37056,12 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
@@ -37148,14 +37148,14 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>C. LEAL FLORES</t>
+          <t>M. MARTINEZ MAJAN</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
@@ -37169,7 +37169,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H60" s="8" t="n">
@@ -37185,7 +37185,7 @@
         <v>0</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>0.5319</v>
+        <v>0.3623</v>
       </c>
       <c r="M60" s="9" t="n">
         <v>0.7246</v>
@@ -37202,7 +37202,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>B. ARMENGOL VALL</t>
+          <t>C. LEAL FLORES</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
@@ -37239,7 +37239,7 @@
         <v>0</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>0.3623</v>
+        <v>0.5319</v>
       </c>
       <c r="M61" s="9" t="n">
         <v>0.7246</v>
@@ -37256,14 +37256,14 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>M. MARTINEZ MAJAN</t>
+          <t>B. ARMENGOL VALL</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
@@ -37277,7 +37277,7 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H62" s="8" t="n">

--- a/fulls/full_mestre_lf2a_2026.xlsx
+++ b/fulls/full_mestre_lf2a_2026.xlsx
@@ -35042,18 +35042,18 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>S. LLANOS GASULLA</t>
+          <t>A. IVAN</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -35067,16 +35067,16 @@
         </is>
       </c>
       <c r="H21" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" s="8" t="n">
         <v>-2</v>
       </c>
       <c r="K21" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
         <v>0.8621</v>
@@ -35085,7 +35085,7 @@
         <v>1.1733</v>
       </c>
       <c r="N21" s="10" t="n">
-        <v>0.1567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -35096,7 +35096,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>A. IVAN</t>
+          <t>A. BOBAR</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
@@ -35107,12 +35107,12 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
@@ -35121,7 +35121,7 @@
         </is>
       </c>
       <c r="H22" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="8" t="n">
         <v>0</v>
@@ -35139,7 +35139,7 @@
         <v>1.1733</v>
       </c>
       <c r="N22" s="10" t="n">
-        <v>0</v>
+        <v>0.0784</v>
       </c>
     </row>
     <row r="23">
@@ -35150,41 +35150,41 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>A. BOBAR</t>
+          <t>S. LLANOS GASULLA</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H23" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="8" t="n">
         <v>-2</v>
       </c>
       <c r="K23" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L23" s="9" t="n">
         <v>0.8621</v>
@@ -35193,7 +35193,7 @@
         <v>1.1733</v>
       </c>
       <c r="N23" s="10" t="n">
-        <v>0.0784</v>
+        <v>0.1567</v>
       </c>
     </row>
     <row r="24">
@@ -35474,50 +35474,50 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>N. IPO SERICHE-DOUGAN</t>
+          <t>D. MILIAUSKAITE</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>1.8895</v>
+        <v>2.2109</v>
       </c>
       <c r="M29" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>0.1453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -35582,41 +35582,41 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>P. DE MIER ESPINA</t>
+          <t>N. IPO SERICHE-DOUGAN</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H31" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L31" s="9" t="n">
         <v>1.8895</v>
@@ -35625,7 +35625,7 @@
         <v>0.6</v>
       </c>
       <c r="N31" s="10" t="n">
-        <v>0</v>
+        <v>0.1453</v>
       </c>
     </row>
     <row r="32">
@@ -35636,7 +35636,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>D. MILIAUSKAITE</t>
+          <t>P. DE MIER ESPINA</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
@@ -35647,7 +35647,7 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -35657,7 +35657,7 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H32" s="8" t="n">
@@ -35670,10 +35670,10 @@
         <v>10</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>2.2109</v>
+        <v>1.8895</v>
       </c>
       <c r="M32" s="9" t="n">
         <v>0.6</v>
@@ -36284,7 +36284,7 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>E. FLOREZ PASCUAL</t>
+          <t>M. ARANDA FRAILE</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
@@ -36338,7 +36338,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>M. ARANDA FRAILE</t>
+          <t>C. UGOCHUKWU UGOCHUKWU</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
@@ -36392,7 +36392,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>C. UGOCHUKWU UGOCHUKWU</t>
+          <t>E. FLOREZ PASCUAL</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
@@ -36446,14 +36446,14 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>M. GOMEZ HERNANDEZ</t>
+          <t>A. QUESADA ROMERO</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
         <v>1.2</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
@@ -36462,25 +36462,25 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G47" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H47" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" s="8" t="n">
         <v>3</v>
       </c>
       <c r="K47" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L47" s="9" t="n">
         <v>1</v>
@@ -36500,14 +36500,14 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>A. QUESADA ROMERO</t>
+          <t>M. GOMEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
         <v>1.2</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
@@ -36516,7 +36516,7 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
@@ -36528,13 +36528,13 @@
         <v>0</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="8" t="n">
         <v>3</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L48" s="9" t="n">
         <v>1</v>
@@ -36878,14 +36878,14 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>M. SANMARTÍN FALCÓN</t>
+          <t>L. TESSON</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
@@ -36932,14 +36932,14 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>L. TESSON</t>
+          <t>C. LOUREIRO CURRAS</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
@@ -36948,12 +36948,12 @@
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H56" s="8" t="n">
@@ -36986,14 +36986,14 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>C. LOUREIRO CURRAS</t>
+          <t>S. ANNE BRANS</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
@@ -37002,12 +37002,12 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">
@@ -37040,14 +37040,14 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>M. ANGULO QUINTANA</t>
+          <t>M. SANMARTÍN FALCÓN</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
@@ -37094,7 +37094,7 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>S. ANNE BRANS</t>
+          <t>M. ANGULO QUINTANA</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
@@ -37115,7 +37115,7 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H59" s="8" t="n">
@@ -37202,7 +37202,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>C. LEAL FLORES</t>
+          <t>B. ARMENGOL VALL</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
@@ -37239,7 +37239,7 @@
         <v>0</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>0.5319</v>
+        <v>0.3623</v>
       </c>
       <c r="M61" s="9" t="n">
         <v>0.7246</v>
@@ -37256,7 +37256,7 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>B. ARMENGOL VALL</t>
+          <t>C. LEAL FLORES</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
@@ -37293,7 +37293,7 @@
         <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>0.3623</v>
+        <v>0.5319</v>
       </c>
       <c r="M62" s="9" t="n">
         <v>0.7246</v>

--- a/fulls/full_mestre_lf2a_2026.xlsx
+++ b/fulls/full_mestre_lf2a_2026.xlsx
@@ -35204,28 +35204,28 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>E. CASTRO LUTZARDO</t>
+          <t>N. MARTÍNEZ MARTÍNEZ</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H24" s="8" t="n">
@@ -35258,28 +35258,28 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>N. MARTÍNEZ MARTÍNEZ</t>
+          <t>S. TORRUELLA BRETÓN</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H25" s="8" t="n">
@@ -35292,7 +35292,7 @@
         <v>2</v>
       </c>
       <c r="K25" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L25" s="9" t="n">
         <v>1.1733</v>
@@ -35312,14 +35312,14 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>S. TORRUELLA BRETÓN</t>
+          <t>E. CASTRO LUTZARDO</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
@@ -35328,12 +35328,12 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H26" s="8" t="n">
@@ -35346,7 +35346,7 @@
         <v>2</v>
       </c>
       <c r="K26" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L26" s="9" t="n">
         <v>1.1733</v>
@@ -35474,7 +35474,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>D. MILIAUSKAITE</t>
+          <t>P. DE MIER ESPINA</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
@@ -35485,7 +35485,7 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -35495,7 +35495,7 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H29" s="8" t="n">
@@ -35508,10 +35508,10 @@
         <v>10</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>2.2109</v>
+        <v>1.8895</v>
       </c>
       <c r="M29" s="9" t="n">
         <v>0.6</v>
@@ -35636,7 +35636,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>P. DE MIER ESPINA</t>
+          <t>D. MILIAUSKAITE</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
@@ -35647,7 +35647,7 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -35657,7 +35657,7 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H32" s="8" t="n">
@@ -35670,10 +35670,10 @@
         <v>10</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>1.8895</v>
+        <v>2.2109</v>
       </c>
       <c r="M32" s="9" t="n">
         <v>0.6</v>
@@ -36338,7 +36338,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>C. UGOCHUKWU UGOCHUKWU</t>
+          <t>E. FLOREZ PASCUAL</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
@@ -36392,7 +36392,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>E. FLOREZ PASCUAL</t>
+          <t>C. UGOCHUKWU UGOCHUKWU</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
@@ -36446,14 +36446,14 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>A. QUESADA ROMERO</t>
+          <t>M. GOMEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
         <v>1.2</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
@@ -36474,13 +36474,13 @@
         <v>0</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" s="8" t="n">
         <v>3</v>
       </c>
       <c r="K47" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L47" s="9" t="n">
         <v>1</v>
@@ -36500,14 +36500,14 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>M. GOMEZ HERNANDEZ</t>
+          <t>A. QUESADA ROMERO</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
         <v>1.2</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
@@ -36516,25 +36516,25 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H48" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" s="8" t="n">
         <v>3</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L48" s="9" t="n">
         <v>1</v>
@@ -36878,7 +36878,7 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>L. TESSON</t>
+          <t>M. ANGULO QUINTANA</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
@@ -36932,7 +36932,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>C. LOUREIRO CURRAS</t>
+          <t>M. SANMARTÍN FALCÓN</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
@@ -36948,7 +36948,7 @@
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
@@ -36986,7 +36986,7 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>S. ANNE BRANS</t>
+          <t>L. TESSON</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
@@ -37007,7 +37007,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">
@@ -37040,7 +37040,7 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>M. SANMARTÍN FALCÓN</t>
+          <t>C. LOUREIRO CURRAS</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
@@ -37056,7 +37056,7 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
@@ -37094,7 +37094,7 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>M. ANGULO QUINTANA</t>
+          <t>S. ANNE BRANS</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
@@ -37115,7 +37115,7 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H59" s="8" t="n">
@@ -37148,14 +37148,14 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>M. MARTINEZ MAJAN</t>
+          <t>C. LEAL FLORES</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
@@ -37169,7 +37169,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H60" s="8" t="n">
@@ -37185,7 +37185,7 @@
         <v>0</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>0.3623</v>
+        <v>0.5319</v>
       </c>
       <c r="M60" s="9" t="n">
         <v>0.7246</v>
@@ -37202,14 +37202,14 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>B. ARMENGOL VALL</t>
+          <t>M. MARTINEZ MAJAN</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H61" s="8" t="n">
@@ -37256,7 +37256,7 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>C. LEAL FLORES</t>
+          <t>B. ARMENGOL VALL</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
@@ -37293,7 +37293,7 @@
         <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>0.5319</v>
+        <v>0.3623</v>
       </c>
       <c r="M62" s="9" t="n">
         <v>0.7246</v>
@@ -37688,7 +37688,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>C. RAMIREZ MORALES</t>
+          <t>L. GARCIA ANDURA</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
@@ -37742,7 +37742,7 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>L. GARCIA ANDURA</t>
+          <t>C. RAMIREZ MORALES</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">

--- a/fulls/full_mestre_lf2a_2026.xlsx
+++ b/fulls/full_mestre_lf2a_2026.xlsx
@@ -35474,7 +35474,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>P. DE MIER ESPINA</t>
+          <t>D. MILIAUSKAITE</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
@@ -35485,7 +35485,7 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -35495,7 +35495,7 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H29" s="8" t="n">
@@ -35508,10 +35508,10 @@
         <v>10</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>1.8895</v>
+        <v>2.2109</v>
       </c>
       <c r="M29" s="9" t="n">
         <v>0.6</v>
@@ -35582,41 +35582,41 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>N. IPO SERICHE-DOUGAN</t>
+          <t>P. DE MIER ESPINA</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
       <c r="H31" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L31" s="9" t="n">
         <v>1.8895</v>
@@ -35625,7 +35625,7 @@
         <v>0.6</v>
       </c>
       <c r="N31" s="10" t="n">
-        <v>0.1453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -35636,50 +35636,50 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>D. MILIAUSKAITE</t>
+          <t>N. IPO SERICHE-DOUGAN</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
       <c r="H32" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>2.2109</v>
+        <v>1.8895</v>
       </c>
       <c r="M32" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="N32" s="10" t="n">
-        <v>0</v>
+        <v>0.1453</v>
       </c>
     </row>
     <row r="33">
@@ -36284,7 +36284,7 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>M. ARANDA FRAILE</t>
+          <t>C. UGOCHUKWU UGOCHUKWU</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
@@ -36392,7 +36392,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>C. UGOCHUKWU UGOCHUKWU</t>
+          <t>M. ARANDA FRAILE</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
@@ -36446,7 +36446,7 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>M. GOMEZ HERNANDEZ</t>
+          <t>E. ABUBAKAR ARREY</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
@@ -36474,7 +36474,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" s="8" t="n">
         <v>3</v>
@@ -36554,7 +36554,7 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>E. ABUBAKAR ARREY</t>
+          <t>N. GOMEZ COBO</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
@@ -36608,7 +36608,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>N. GOMEZ COBO</t>
+          <t>M. GOMEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
@@ -36636,7 +36636,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="8" t="n">
         <v>3</v>
@@ -36878,7 +36878,7 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>M. ANGULO QUINTANA</t>
+          <t>S. ANNE BRANS</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
@@ -36899,7 +36899,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
@@ -36932,14 +36932,14 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>M. SANMARTÍN FALCÓN</t>
+          <t>L. TESSON</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H56" s="8" t="n">
@@ -36986,14 +36986,14 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>L. TESSON</t>
+          <t>C. LOUREIRO CURRAS</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
@@ -37002,12 +37002,12 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">
@@ -37040,14 +37040,14 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>C. LOUREIRO CURRAS</t>
+          <t>M. ANGULO QUINTANA</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
@@ -37056,12 +37056,12 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
@@ -37094,14 +37094,14 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>S. ANNE BRANS</t>
+          <t>M. SANMARTÍN FALCÓN</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H59" s="8" t="n">
@@ -37148,14 +37148,14 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>C. LEAL FLORES</t>
+          <t>M. MARTINEZ MAJAN</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
@@ -37169,7 +37169,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H60" s="8" t="n">
@@ -37185,7 +37185,7 @@
         <v>0</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>0.5319</v>
+        <v>0.3623</v>
       </c>
       <c r="M60" s="9" t="n">
         <v>0.7246</v>
@@ -37202,14 +37202,14 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>M. MARTINEZ MAJAN</t>
+          <t>B. ARMENGOL VALL</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H61" s="8" t="n">
@@ -37256,7 +37256,7 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>B. ARMENGOL VALL</t>
+          <t>C. LEAL FLORES</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
@@ -37293,7 +37293,7 @@
         <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>0.3623</v>
+        <v>0.5319</v>
       </c>
       <c r="M62" s="9" t="n">
         <v>0.7246</v>
@@ -37310,7 +37310,7 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>M. TSONEVA</t>
+          <t>S. FRANCISCO ABOS</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
@@ -37331,7 +37331,7 @@
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H63" s="8" t="n">
@@ -37341,16 +37341,16 @@
         <v>0</v>
       </c>
       <c r="J63" s="8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K63" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>0.3623</v>
+        <v>1.1364</v>
       </c>
       <c r="M63" s="9" t="n">
-        <v>0.431</v>
+        <v>1.0638</v>
       </c>
       <c r="N63" s="10" t="n">
         <v>0</v>
@@ -37364,7 +37364,7 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>S. FRANCISCO ABOS</t>
+          <t>M. TSONEVA</t>
         </is>
       </c>
       <c r="C64" s="8" t="n">
@@ -37385,7 +37385,7 @@
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H64" s="8" t="n">
@@ -37395,16 +37395,16 @@
         <v>0</v>
       </c>
       <c r="J64" s="8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K64" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>1.1364</v>
+        <v>0.3623</v>
       </c>
       <c r="M64" s="9" t="n">
-        <v>1.0638</v>
+        <v>0.431</v>
       </c>
       <c r="N64" s="10" t="n">
         <v>0</v>
@@ -37688,7 +37688,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>L. GARCIA ANDURA</t>
+          <t>C. RAMIREZ MORALES</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
@@ -37742,7 +37742,7 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>C. RAMIREZ MORALES</t>
+          <t>L. GARCIA ANDURA</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">

--- a/fulls/full_mestre_lf2a_2026.xlsx
+++ b/fulls/full_mestre_lf2a_2026.xlsx
@@ -35042,7 +35042,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>A. IVAN</t>
+          <t>A. BOBAR</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
@@ -35053,12 +35053,12 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -35067,7 +35067,7 @@
         </is>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="8" t="n">
         <v>0</v>
@@ -35085,7 +35085,7 @@
         <v>1.1733</v>
       </c>
       <c r="N21" s="10" t="n">
-        <v>0</v>
+        <v>0.0784</v>
       </c>
     </row>
     <row r="22">
@@ -35096,41 +35096,41 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>A. BOBAR</t>
+          <t>S. LLANOS GASULLA</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="8" t="n">
         <v>-2</v>
       </c>
       <c r="K22" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L22" s="9" t="n">
         <v>0.8621</v>
@@ -35139,7 +35139,7 @@
         <v>1.1733</v>
       </c>
       <c r="N22" s="10" t="n">
-        <v>0.0784</v>
+        <v>0.1567</v>
       </c>
     </row>
     <row r="23">
@@ -35150,18 +35150,18 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>S. LLANOS GASULLA</t>
+          <t>A. IVAN</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -35175,16 +35175,16 @@
         </is>
       </c>
       <c r="H23" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J23" s="8" t="n">
         <v>-2</v>
       </c>
       <c r="K23" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L23" s="9" t="n">
         <v>0.8621</v>
@@ -35193,7 +35193,7 @@
         <v>1.1733</v>
       </c>
       <c r="N23" s="10" t="n">
-        <v>0.1567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -35204,18 +35204,18 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>N. MARTÍNEZ MARTÍNEZ</t>
+          <t>E. CASTRO LUTZARDO</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -35225,7 +35225,7 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H24" s="8" t="n">
@@ -35312,28 +35312,28 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>E. CASTRO LUTZARDO</t>
+          <t>N. MARTÍNEZ MARTÍNEZ</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H26" s="8" t="n">
@@ -35528,18 +35528,18 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>N. PADROSA MONS</t>
+          <t>P. DE MIER ESPINA</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -35562,7 +35562,7 @@
         <v>10</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L30" s="9" t="n">
         <v>1.8895</v>
@@ -35582,18 +35582,18 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>P. DE MIER ESPINA</t>
+          <t>N. PADROSA MONS</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -35616,7 +35616,7 @@
         <v>10</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L31" s="9" t="n">
         <v>1.8895</v>
@@ -36446,7 +36446,7 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>E. ABUBAKAR ARREY</t>
+          <t>N. GOMEZ COBO</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
@@ -36500,14 +36500,14 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>A. QUESADA ROMERO</t>
+          <t>E. ABUBAKAR ARREY</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
         <v>1.2</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
@@ -36516,7 +36516,7 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
@@ -36534,7 +36534,7 @@
         <v>3</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L48" s="9" t="n">
         <v>1</v>
@@ -36554,14 +36554,14 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>N. GOMEZ COBO</t>
+          <t>A. QUESADA ROMERO</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
         <v>1.2</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
@@ -36570,7 +36570,7 @@
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
@@ -36588,7 +36588,7 @@
         <v>3</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L49" s="9" t="n">
         <v>1</v>
@@ -36932,14 +36932,14 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>L. TESSON</t>
+          <t>C. LOUREIRO CURRAS</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
@@ -36948,12 +36948,12 @@
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H56" s="8" t="n">
@@ -36986,14 +36986,14 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>C. LOUREIRO CURRAS</t>
+          <t>L. TESSON</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
@@ -37002,12 +37002,12 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">
@@ -37310,7 +37310,7 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>S. FRANCISCO ABOS</t>
+          <t>M. TSONEVA</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
@@ -37331,7 +37331,7 @@
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H63" s="8" t="n">
@@ -37341,16 +37341,16 @@
         <v>0</v>
       </c>
       <c r="J63" s="8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K63" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>1.1364</v>
+        <v>0.3623</v>
       </c>
       <c r="M63" s="9" t="n">
-        <v>1.0638</v>
+        <v>0.431</v>
       </c>
       <c r="N63" s="10" t="n">
         <v>0</v>
@@ -37364,7 +37364,7 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>M. TSONEVA</t>
+          <t>S. FRANCISCO ABOS</t>
         </is>
       </c>
       <c r="C64" s="8" t="n">
@@ -37385,7 +37385,7 @@
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H64" s="8" t="n">
@@ -37395,16 +37395,16 @@
         <v>0</v>
       </c>
       <c r="J64" s="8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K64" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>0.3623</v>
+        <v>1.1364</v>
       </c>
       <c r="M64" s="9" t="n">
-        <v>0.431</v>
+        <v>1.0638</v>
       </c>
       <c r="N64" s="10" t="n">
         <v>0</v>

--- a/fulls/full_mestre_lf2a_2026.xlsx
+++ b/fulls/full_mestre_lf2a_2026.xlsx
@@ -47723,7 +47723,7 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>E. ABUBAKAR ARREY</t>
+          <t>M. GOMEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
@@ -47751,7 +47751,7 @@
         <v>0</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" s="8" t="n">
         <v>3</v>
@@ -47777,7 +47777,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>N. GOMEZ COBO</t>
+          <t>E. ABUBAKAR ARREY</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
@@ -47885,7 +47885,7 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>M. GOMEZ HERNANDEZ</t>
+          <t>N. GOMEZ COBO</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
@@ -47913,7 +47913,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" s="8" t="n">
         <v>3</v>
@@ -48101,7 +48101,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>M. ANGULO QUINTANA</t>
+          <t>S. ANNE BRANS</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -48122,7 +48122,7 @@
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H66" s="8" t="n">
@@ -48209,7 +48209,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>S. ANNE BRANS</t>
+          <t>M. ANGULO QUINTANA</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H68" s="8" t="n">
@@ -48263,14 +48263,14 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>L. TESSON</t>
+          <t>C. LOUREIRO CURRAS</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
@@ -48279,12 +48279,12 @@
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H69" s="8" t="n">
@@ -48317,14 +48317,14 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>C. LOUREIRO CURRAS</t>
+          <t>L. TESSON</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
@@ -48333,12 +48333,12 @@
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H70" s="8" t="n">

--- a/fulls/full_mestre_lf2a_2026.xlsx
+++ b/fulls/full_mestre_lf2a_2026.xlsx
@@ -46049,14 +46049,14 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>E. CASTRO LUTZARDO</t>
+          <t>S. TORRUELLA BRETÓN</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
@@ -46065,12 +46065,12 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H28" s="8" t="n">
@@ -46083,7 +46083,7 @@
         <v>2</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L28" s="9" t="n">
         <v>1.1733</v>
@@ -46103,14 +46103,14 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>S. TORRUELLA BRETÓN</t>
+          <t>E. CASTRO LUTZARDO</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
@@ -46119,12 +46119,12 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H29" s="8" t="n">
@@ -46137,7 +46137,7 @@
         <v>2</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
         <v>1.1733</v>
@@ -46373,41 +46373,41 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>P. DE MIER ESPINA</t>
+          <t>N. IPO SERICHE-DOUGAN</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H34" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K34" s="10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L34" s="9" t="n">
         <v>1.8895</v>
@@ -46416,7 +46416,7 @@
         <v>0.6</v>
       </c>
       <c r="N34" s="10" t="n">
-        <v>0</v>
+        <v>0.1453</v>
       </c>
     </row>
     <row r="35">
@@ -46535,41 +46535,41 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>N. IPO SERICHE-DOUGAN</t>
+          <t>P. DE MIER ESPINA</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
       <c r="H37" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>1.8895</v>
@@ -46578,7 +46578,7 @@
         <v>0.6</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>0.1453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -46697,18 +46697,18 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>B. ARMENGOL VALL</t>
+          <t>C. LEAL FLORES</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -46725,22 +46725,22 @@
         <v>1</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.9291</v>
+        <v>1.0036</v>
       </c>
       <c r="M40" s="9" t="n">
         <v>0.7991</v>
       </c>
       <c r="N40" s="10" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.0912</v>
       </c>
     </row>
     <row r="41">
@@ -46751,50 +46751,50 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>C. LEAL FLORES</t>
+          <t>B. ARMENGOL VALL</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H41" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L41" s="9" t="n">
-        <v>1.0036</v>
+        <v>0.9291</v>
       </c>
       <c r="M41" s="9" t="n">
         <v>0.7991</v>
       </c>
       <c r="N41" s="10" t="n">
-        <v>0.0912</v>
+        <v>0.08450000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -47777,7 +47777,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>E. ABUBAKAR ARREY</t>
+          <t>N. GOMEZ COBO</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
@@ -47831,14 +47831,14 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>A. QUESADA ROMERO</t>
+          <t>E. ABUBAKAR ARREY</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
         <v>1.2</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
@@ -47865,7 +47865,7 @@
         <v>3</v>
       </c>
       <c r="K61" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L61" s="9" t="n">
         <v>1</v>
@@ -47885,14 +47885,14 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>N. GOMEZ COBO</t>
+          <t>A. QUESADA ROMERO</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
         <v>1.2</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
@@ -47901,7 +47901,7 @@
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
@@ -47919,7 +47919,7 @@
         <v>3</v>
       </c>
       <c r="K62" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L62" s="9" t="n">
         <v>1</v>
@@ -48101,7 +48101,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>S. ANNE BRANS</t>
+          <t>L. TESSON</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -48122,7 +48122,7 @@
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H66" s="8" t="n">
@@ -48155,7 +48155,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>M. SANMARTÍN FALCÓN</t>
+          <t>C. LOUREIRO CURRAS</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
@@ -48171,7 +48171,7 @@
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
@@ -48209,14 +48209,14 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>M. ANGULO QUINTANA</t>
+          <t>M. SANMARTÍN FALCÓN</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
@@ -48230,7 +48230,7 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H68" s="8" t="n">
@@ -48263,14 +48263,14 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>C. LOUREIRO CURRAS</t>
+          <t>S. ANNE BRANS</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
@@ -48279,12 +48279,12 @@
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H69" s="8" t="n">
@@ -48317,7 +48317,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>L. TESSON</t>
+          <t>M. ANGULO QUINTANA</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">

--- a/fulls/full_mestre_lf2a_2026.xlsx
+++ b/fulls/full_mestre_lf2a_2026.xlsx
@@ -46049,14 +46049,14 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>S. TORRUELLA BRETÓN</t>
+          <t>E. CASTRO LUTZARDO</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
@@ -46065,12 +46065,12 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H28" s="8" t="n">
@@ -46083,7 +46083,7 @@
         <v>2</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
         <v>1.1733</v>
@@ -46103,14 +46103,14 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>E. CASTRO LUTZARDO</t>
+          <t>S. TORRUELLA BRETÓN</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
@@ -46119,12 +46119,12 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H29" s="8" t="n">
@@ -46137,7 +46137,7 @@
         <v>2</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L29" s="9" t="n">
         <v>1.1733</v>
@@ -46373,14 +46373,14 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>N. IPO SERICHE-DOUGAN</t>
+          <t>N. PADROSA MONS</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
@@ -46398,16 +46398,16 @@
         </is>
       </c>
       <c r="H34" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K34" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L34" s="9" t="n">
         <v>1.8895</v>
@@ -46416,7 +46416,7 @@
         <v>0.6</v>
       </c>
       <c r="N34" s="10" t="n">
-        <v>0.1453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -46427,7 +46427,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>D. MILIAUSKAITE</t>
+          <t>P. DE MIER ESPINA</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -46438,7 +46438,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -46448,7 +46448,7 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H35" s="8" t="n">
@@ -46461,10 +46461,10 @@
         <v>10</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>2.2109</v>
+        <v>1.8895</v>
       </c>
       <c r="M35" s="9" t="n">
         <v>0.6</v>
@@ -46481,28 +46481,28 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>N. PADROSA MONS</t>
+          <t>D. MILIAUSKAITE</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H36" s="8" t="n">
@@ -46518,7 +46518,7 @@
         <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>1.8895</v>
+        <v>2.2109</v>
       </c>
       <c r="M36" s="9" t="n">
         <v>0.6</v>
@@ -46535,41 +46535,41 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>P. DE MIER ESPINA</t>
+          <t>N. IPO SERICHE-DOUGAN</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H37" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>1.8895</v>
@@ -46578,7 +46578,7 @@
         <v>0.6</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>0</v>
+        <v>0.1453</v>
       </c>
     </row>
     <row r="38">
@@ -47723,14 +47723,14 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>M. GOMEZ HERNANDEZ</t>
+          <t>A. QUESADA ROMERO</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
         <v>1.2</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
@@ -47739,25 +47739,25 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G59" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H59" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" s="8" t="n">
         <v>3</v>
       </c>
       <c r="K59" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L59" s="9" t="n">
         <v>1</v>
@@ -47777,7 +47777,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>N. GOMEZ COBO</t>
+          <t>E. ABUBAKAR ARREY</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
@@ -47831,7 +47831,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>E. ABUBAKAR ARREY</t>
+          <t>M. GOMEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
@@ -47859,7 +47859,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" s="8" t="n">
         <v>3</v>
@@ -47885,14 +47885,14 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>A. QUESADA ROMERO</t>
+          <t>N. GOMEZ COBO</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
         <v>1.2</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
@@ -47901,7 +47901,7 @@
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
@@ -47919,7 +47919,7 @@
         <v>3</v>
       </c>
       <c r="K62" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
         <v>1</v>
@@ -48101,7 +48101,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>L. TESSON</t>
+          <t>S. ANNE BRANS</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -48122,7 +48122,7 @@
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H66" s="8" t="n">
@@ -48155,14 +48155,14 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>C. LOUREIRO CURRAS</t>
+          <t>M. ANGULO QUINTANA</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
@@ -48171,12 +48171,12 @@
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H67" s="8" t="n">
@@ -48209,7 +48209,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>M. SANMARTÍN FALCÓN</t>
+          <t>C. LOUREIRO CURRAS</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
@@ -48225,7 +48225,7 @@
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
@@ -48263,7 +48263,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>S. ANNE BRANS</t>
+          <t>L. TESSON</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
@@ -48284,7 +48284,7 @@
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H69" s="8" t="n">
@@ -48317,14 +48317,14 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>M. ANGULO QUINTANA</t>
+          <t>M. SANMARTÍN FALCÓN</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H70" s="8" t="n">

--- a/fulls/full_mestre_lf2a_2026.xlsx
+++ b/fulls/full_mestre_lf2a_2026.xlsx
@@ -46049,14 +46049,14 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>E. CASTRO LUTZARDO</t>
+          <t>S. TORRUELLA BRETÓN</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
@@ -46065,12 +46065,12 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H28" s="8" t="n">
@@ -46083,7 +46083,7 @@
         <v>2</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L28" s="9" t="n">
         <v>1.1733</v>
@@ -46103,14 +46103,14 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>S. TORRUELLA BRETÓN</t>
+          <t>E. CASTRO LUTZARDO</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
@@ -46119,12 +46119,12 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H29" s="8" t="n">
@@ -46137,7 +46137,7 @@
         <v>2</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
         <v>1.1733</v>
@@ -46373,18 +46373,18 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>N. PADROSA MONS</t>
+          <t>P. DE MIER ESPINA</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -46407,7 +46407,7 @@
         <v>10</v>
       </c>
       <c r="K34" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L34" s="9" t="n">
         <v>1.8895</v>
@@ -46427,7 +46427,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>P. DE MIER ESPINA</t>
+          <t>D. MILIAUSKAITE</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -46438,7 +46438,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -46448,7 +46448,7 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H35" s="8" t="n">
@@ -46461,10 +46461,10 @@
         <v>10</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>1.8895</v>
+        <v>2.2109</v>
       </c>
       <c r="M35" s="9" t="n">
         <v>0.6</v>
@@ -46481,50 +46481,50 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>D. MILIAUSKAITE</t>
+          <t>N. IPO SERICHE-DOUGAN</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
       <c r="H36" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>2.2109</v>
+        <v>1.8895</v>
       </c>
       <c r="M36" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>0</v>
+        <v>0.1453</v>
       </c>
     </row>
     <row r="37">
@@ -46535,14 +46535,14 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>N. IPO SERICHE-DOUGAN</t>
+          <t>N. PADROSA MONS</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
@@ -46551,7 +46551,7 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
@@ -46560,16 +46560,16 @@
         </is>
       </c>
       <c r="H37" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>1.8895</v>
@@ -46578,7 +46578,7 @@
         <v>0.6</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>0.1453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -47777,7 +47777,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>E. ABUBAKAR ARREY</t>
+          <t>N. GOMEZ COBO</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
@@ -47831,7 +47831,7 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>M. GOMEZ HERNANDEZ</t>
+          <t>E. ABUBAKAR ARREY</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
@@ -47859,7 +47859,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" s="8" t="n">
         <v>3</v>
@@ -47885,7 +47885,7 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>N. GOMEZ COBO</t>
+          <t>M. GOMEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
@@ -47913,7 +47913,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="8" t="n">
         <v>3</v>
@@ -48101,7 +48101,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>S. ANNE BRANS</t>
+          <t>M. ANGULO QUINTANA</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -48122,7 +48122,7 @@
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H66" s="8" t="n">
@@ -48155,7 +48155,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>M. ANGULO QUINTANA</t>
+          <t>S. ANNE BRANS</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
@@ -48176,7 +48176,7 @@
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H67" s="8" t="n">
@@ -48209,14 +48209,14 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>C. LOUREIRO CURRAS</t>
+          <t>L. TESSON</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
@@ -48225,12 +48225,12 @@
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H68" s="8" t="n">
@@ -48263,14 +48263,14 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>L. TESSON</t>
+          <t>C. LOUREIRO CURRAS</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
@@ -48279,12 +48279,12 @@
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H69" s="8" t="n">

--- a/fulls/full_mestre_lf2a_2026.xlsx
+++ b/fulls/full_mestre_lf2a_2026.xlsx
@@ -45995,18 +45995,18 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>N. MARTÍNEZ MARTÍNEZ</t>
+          <t>E. CASTRO LUTZARDO</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -46016,7 +46016,7 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H27" s="8" t="n">
@@ -46049,28 +46049,28 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>S. TORRUELLA BRETÓN</t>
+          <t>N. MARTÍNEZ MARTÍNEZ</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H28" s="8" t="n">
@@ -46083,7 +46083,7 @@
         <v>2</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
         <v>1.1733</v>
@@ -46103,14 +46103,14 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>E. CASTRO LUTZARDO</t>
+          <t>S. TORRUELLA BRETÓN</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
@@ -46119,12 +46119,12 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H29" s="8" t="n">
@@ -46137,7 +46137,7 @@
         <v>2</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L29" s="9" t="n">
         <v>1.1733</v>
@@ -46373,7 +46373,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>P. DE MIER ESPINA</t>
+          <t>D. MILIAUSKAITE</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
@@ -46384,7 +46384,7 @@
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -46394,7 +46394,7 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H34" s="8" t="n">
@@ -46407,10 +46407,10 @@
         <v>10</v>
       </c>
       <c r="K34" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>1.8895</v>
+        <v>2.2109</v>
       </c>
       <c r="M34" s="9" t="n">
         <v>0.6</v>
@@ -46427,50 +46427,50 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>D. MILIAUSKAITE</t>
+          <t>N. IPO SERICHE-DOUGAN</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
       <c r="H35" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>2.2109</v>
+        <v>1.8895</v>
       </c>
       <c r="M35" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>0</v>
+        <v>0.1453</v>
       </c>
     </row>
     <row r="36">
@@ -46481,41 +46481,41 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>N. IPO SERICHE-DOUGAN</t>
+          <t>P. DE MIER ESPINA</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
       <c r="H36" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L36" s="9" t="n">
         <v>1.8895</v>
@@ -46524,7 +46524,7 @@
         <v>0.6</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>0.1453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -47723,14 +47723,14 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>A. QUESADA ROMERO</t>
+          <t>N. GOMEZ COBO</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
         <v>1.2</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
@@ -47739,7 +47739,7 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
@@ -47757,7 +47757,7 @@
         <v>3</v>
       </c>
       <c r="K59" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L59" s="9" t="n">
         <v>1</v>
@@ -47777,7 +47777,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>N. GOMEZ COBO</t>
+          <t>E. ABUBAKAR ARREY</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
@@ -47831,14 +47831,14 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>E. ABUBAKAR ARREY</t>
+          <t>A. QUESADA ROMERO</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
         <v>1.2</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
@@ -47865,7 +47865,7 @@
         <v>3</v>
       </c>
       <c r="K61" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L61" s="9" t="n">
         <v>1</v>
@@ -48101,14 +48101,14 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>M. ANGULO QUINTANA</t>
+          <t>C. LOUREIRO CURRAS</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
@@ -48117,12 +48117,12 @@
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H66" s="8" t="n">
@@ -48155,7 +48155,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>S. ANNE BRANS</t>
+          <t>L. TESSON</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
@@ -48176,7 +48176,7 @@
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H67" s="8" t="n">
@@ -48209,14 +48209,14 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>L. TESSON</t>
+          <t>M. SANMARTÍN FALCÓN</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
@@ -48230,7 +48230,7 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H68" s="8" t="n">
@@ -48263,14 +48263,14 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>C. LOUREIRO CURRAS</t>
+          <t>S. ANNE BRANS</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
@@ -48279,12 +48279,12 @@
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H69" s="8" t="n">
@@ -48317,14 +48317,14 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>M. SANMARTÍN FALCÓN</t>
+          <t>M. ANGULO QUINTANA</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H70" s="8" t="n">

--- a/fulls/full_mestre_lf2a_2026.xlsx
+++ b/fulls/full_mestre_lf2a_2026.xlsx
@@ -46373,18 +46373,18 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>D. MILIAUSKAITE</t>
+          <t>N. PADROSA MONS</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -46394,7 +46394,7 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H34" s="8" t="n">
@@ -46410,7 +46410,7 @@
         <v>0</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>2.2109</v>
+        <v>1.8895</v>
       </c>
       <c r="M34" s="9" t="n">
         <v>0.6</v>
@@ -46427,41 +46427,41 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>N. IPO SERICHE-DOUGAN</t>
+          <t>P. DE MIER ESPINA</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
       <c r="H35" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L35" s="9" t="n">
         <v>1.8895</v>
@@ -46470,7 +46470,7 @@
         <v>0.6</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>0.1453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -46481,41 +46481,41 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>P. DE MIER ESPINA</t>
+          <t>N. IPO SERICHE-DOUGAN</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H36" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L36" s="9" t="n">
         <v>1.8895</v>
@@ -46524,7 +46524,7 @@
         <v>0.6</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>0</v>
+        <v>0.1453</v>
       </c>
     </row>
     <row r="37">
@@ -46535,28 +46535,28 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>N. PADROSA MONS</t>
+          <t>D. MILIAUSKAITE</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H37" s="8" t="n">
@@ -46572,7 +46572,7 @@
         <v>0</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>1.8895</v>
+        <v>2.2109</v>
       </c>
       <c r="M37" s="9" t="n">
         <v>0.6</v>
@@ -47777,7 +47777,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>E. ABUBAKAR ARREY</t>
+          <t>M. GOMEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
@@ -47805,7 +47805,7 @@
         <v>0</v>
       </c>
       <c r="I60" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="8" t="n">
         <v>3</v>
@@ -47831,14 +47831,14 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>A. QUESADA ROMERO</t>
+          <t>E. ABUBAKAR ARREY</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
         <v>1.2</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
@@ -47865,7 +47865,7 @@
         <v>3</v>
       </c>
       <c r="K61" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L61" s="9" t="n">
         <v>1</v>
@@ -47885,14 +47885,14 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>M. GOMEZ HERNANDEZ</t>
+          <t>A. QUESADA ROMERO</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
         <v>1.2</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
@@ -47901,25 +47901,25 @@
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G62" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H62" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" s="8" t="n">
         <v>3</v>
       </c>
       <c r="K62" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L62" s="9" t="n">
         <v>1</v>
@@ -48101,14 +48101,14 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>C. LOUREIRO CURRAS</t>
+          <t>M. ANGULO QUINTANA</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
@@ -48117,12 +48117,12 @@
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H66" s="8" t="n">
@@ -48317,14 +48317,14 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>M. ANGULO QUINTANA</t>
+          <t>C. LOUREIRO CURRAS</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
@@ -48333,12 +48333,12 @@
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H70" s="8" t="n">

--- a/fulls/full_mestre_lf2a_2026.xlsx
+++ b/fulls/full_mestre_lf2a_2026.xlsx
@@ -54206,41 +54206,41 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>A. BOBAR</t>
+          <t>S. LLANOS GASULLA</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>7</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H37" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>0</v>
+        <v>0.4286</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>0.7756999999999999</v>
@@ -54249,7 +54249,7 @@
         <v>0.9358</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>0.0597</v>
+        <v>0.1193</v>
       </c>
     </row>
     <row r="38">
@@ -54260,23 +54260,23 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>S. LLANOS GASULLA</t>
+          <t>A. BOBAR</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
         <v>7</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
@@ -54285,16 +54285,16 @@
         </is>
       </c>
       <c r="H38" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K38" s="10" t="n">
-        <v>0.4286</v>
+        <v>0</v>
       </c>
       <c r="L38" s="9" t="n">
         <v>0.7756999999999999</v>
@@ -54303,7 +54303,7 @@
         <v>0.9358</v>
       </c>
       <c r="N38" s="10" t="n">
-        <v>0.1193</v>
+        <v>0.0597</v>
       </c>
     </row>
     <row r="39">
@@ -54800,32 +54800,32 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>C. LOUREIRO CURRAS</t>
+          <t>M. ANGULO QUINTANA</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="H48" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" s="8" t="n">
         <v>0</v>
@@ -54834,7 +54834,7 @@
         <v>3</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>0.5833</v>
+        <v>0</v>
       </c>
       <c r="L48" s="9" t="n">
         <v>1.0703</v>
@@ -54843,7 +54843,7 @@
         <v>0.9549</v>
       </c>
       <c r="N48" s="10" t="n">
-        <v>0.0765</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -54854,14 +54854,14 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>M. ANGULO QUINTANA</t>
+          <t>L. TESSON</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
@@ -54870,12 +54870,12 @@
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H49" s="8" t="n">
@@ -54908,32 +54908,32 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>L. TESSON</t>
+          <t>C. LOUREIRO CURRAS</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H50" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" s="8" t="n">
         <v>0</v>
@@ -54942,7 +54942,7 @@
         <v>3</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>0</v>
+        <v>0.5833</v>
       </c>
       <c r="L50" s="9" t="n">
         <v>1.0703</v>
@@ -54951,7 +54951,7 @@
         <v>0.9549</v>
       </c>
       <c r="N50" s="10" t="n">
-        <v>0</v>
+        <v>0.0765</v>
       </c>
     </row>
     <row r="51">
@@ -55502,18 +55502,18 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>G. JORGE GARCIA</t>
+          <t>A. DÉNES</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
         <v>4.3</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -55523,7 +55523,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H61" s="8" t="n">
@@ -55556,18 +55556,18 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>A. DÉNES</t>
+          <t>G. JORGE GARCIA</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
         <v>4.3</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
@@ -55577,7 +55577,7 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H62" s="8" t="n">
@@ -55610,14 +55610,14 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>C. MATO DE PRADA</t>
+          <t>M. LLORENTE RUIZ</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
         <v>4.3</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
@@ -55631,11 +55631,11 @@
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H63" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" s="8" t="n">
         <v>0</v>
@@ -55653,7 +55653,7 @@
         <v>0.5708</v>
       </c>
       <c r="N63" s="10" t="n">
-        <v>0</v>
+        <v>0.2049</v>
       </c>
     </row>
     <row r="64">
@@ -55664,14 +55664,14 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>M. LLORENTE RUIZ</t>
+          <t>C. MATO DE PRADA</t>
         </is>
       </c>
       <c r="C64" s="8" t="n">
         <v>4.3</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
@@ -55685,11 +55685,11 @@
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H64" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" s="8" t="n">
         <v>0</v>
@@ -55707,7 +55707,7 @@
         <v>0.5708</v>
       </c>
       <c r="N64" s="10" t="n">
-        <v>0.2049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -55934,18 +55934,18 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>E. LARSEN</t>
+          <t>L. KIEFER</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
@@ -55955,7 +55955,7 @@
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H69" s="8" t="n">
@@ -55968,7 +55968,7 @@
         <v>3</v>
       </c>
       <c r="K69" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="9" t="n">
         <v>1.4184</v>
@@ -55988,28 +55988,28 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>A. TORNE LABARTA</t>
+          <t>S. FRAILE DIAZ</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H70" s="8" t="n">
@@ -56022,7 +56022,7 @@
         <v>3</v>
       </c>
       <c r="K70" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L70" s="9" t="n">
         <v>1.4184</v>
@@ -56042,28 +56042,28 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>S. FRAILE DIAZ</t>
+          <t>A. TORNE LABARTA</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H71" s="8" t="n">
@@ -56076,7 +56076,7 @@
         <v>3</v>
       </c>
       <c r="K71" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L71" s="9" t="n">
         <v>1.4184</v>
@@ -56096,18 +56096,18 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>L. KIEFER</t>
+          <t>E. LARSEN</t>
         </is>
       </c>
       <c r="C72" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
@@ -56117,7 +56117,7 @@
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H72" s="8" t="n">
@@ -56130,7 +56130,7 @@
         <v>3</v>
       </c>
       <c r="K72" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="9" t="n">
         <v>1.4184</v>
@@ -56150,50 +56150,50 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>D. MILIAUSKAITE</t>
+          <t>N. IPO SERICHE-DOUGAN</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G73" s="8" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
       <c r="H73" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K73" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>2.2109</v>
+        <v>1.8895</v>
       </c>
       <c r="M73" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="N73" s="10" t="n">
-        <v>0</v>
+        <v>0.1453</v>
       </c>
     </row>
     <row r="74">
@@ -56204,50 +56204,50 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>N. IPO SERICHE-DOUGAN</t>
+          <t>D. MILIAUSKAITE</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H74" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K74" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>1.8895</v>
+        <v>2.2109</v>
       </c>
       <c r="M74" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="N74" s="10" t="n">
-        <v>0.1453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">

--- a/fulls/full_mestre_lf2a_2026.xlsx
+++ b/fulls/full_mestre_lf2a_2026.xlsx
@@ -54206,23 +54206,23 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>S. LLANOS GASULLA</t>
+          <t>A. BOBAR</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>7</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
@@ -54231,16 +54231,16 @@
         </is>
       </c>
       <c r="H37" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>0.4286</v>
+        <v>0</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>0.7756999999999999</v>
@@ -54249,7 +54249,7 @@
         <v>0.9358</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>0.1193</v>
+        <v>0.0597</v>
       </c>
     </row>
     <row r="38">
@@ -54260,41 +54260,41 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>A. BOBAR</t>
+          <t>S. LLANOS GASULLA</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
         <v>7</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H38" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J38" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K38" s="10" t="n">
-        <v>0</v>
+        <v>0.4286</v>
       </c>
       <c r="L38" s="9" t="n">
         <v>0.7756999999999999</v>
@@ -54303,7 +54303,7 @@
         <v>0.9358</v>
       </c>
       <c r="N38" s="10" t="n">
-        <v>0.0597</v>
+        <v>0.1193</v>
       </c>
     </row>
     <row r="39">
@@ -54800,32 +54800,32 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>M. ANGULO QUINTANA</t>
+          <t>C. LOUREIRO CURRAS</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" s="8" t="n">
         <v>0</v>
@@ -54834,7 +54834,7 @@
         <v>3</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>0</v>
+        <v>0.5833</v>
       </c>
       <c r="L48" s="9" t="n">
         <v>1.0703</v>
@@ -54843,7 +54843,7 @@
         <v>0.9549</v>
       </c>
       <c r="N48" s="10" t="n">
-        <v>0</v>
+        <v>0.0765</v>
       </c>
     </row>
     <row r="49">
@@ -54908,32 +54908,32 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>C. LOUREIRO CURRAS</t>
+          <t>M. ANGULO QUINTANA</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="H50" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" s="8" t="n">
         <v>0</v>
@@ -54942,7 +54942,7 @@
         <v>3</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>0.5833</v>
+        <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
         <v>1.0703</v>
@@ -54951,7 +54951,7 @@
         <v>0.9549</v>
       </c>
       <c r="N50" s="10" t="n">
-        <v>0.0765</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -55124,18 +55124,18 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>C. DE LA OLIVA MARÍN</t>
+          <t>A. BALLESTEROS MELGAR</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -55145,14 +55145,14 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H54" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="8" t="n">
         <v>-1</v>
@@ -55178,18 +55178,18 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>A. BALLESTEROS MELGAR</t>
+          <t>C. DE LA OLIVA MARÍN</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -55199,14 +55199,14 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" s="8" t="n">
         <v>-1</v>
@@ -55340,7 +55340,7 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>H. DIAGNE EHEMBA</t>
+          <t>R. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
@@ -55361,14 +55361,14 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" s="8" t="n">
         <v>1</v>
@@ -55394,7 +55394,7 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>R. GARCIA GARCIA</t>
+          <t>H. DIAGNE EHEMBA</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
@@ -55415,14 +55415,14 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H59" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" s="8" t="n">
         <v>1</v>
@@ -55502,18 +55502,18 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>A. DÉNES</t>
+          <t>G. JORGE GARCIA</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
         <v>4.3</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -55523,7 +55523,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H61" s="8" t="n">
@@ -55556,18 +55556,18 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>G. JORGE GARCIA</t>
+          <t>A. DÉNES</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
         <v>4.3</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
@@ -55577,7 +55577,7 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H62" s="8" t="n">
@@ -55772,7 +55772,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>A. MBENGUE SÁNCHEZ</t>
+          <t>M. OCURTO MENDES</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -55783,7 +55783,7 @@
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
@@ -55826,7 +55826,7 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>M. OCURTO MENDES</t>
+          <t>L. PEREZ CASTRO</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
@@ -55837,12 +55837,12 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
-        </is>
-      </c>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
@@ -55880,7 +55880,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>L. PEREZ CASTRO</t>
+          <t>A. MBENGUE SÁNCHEZ</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
@@ -55896,7 +55896,7 @@
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
@@ -55934,7 +55934,7 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>L. KIEFER</t>
+          <t>S. FRAILE DIAZ</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
@@ -55945,17 +55945,17 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H69" s="8" t="n">
@@ -55968,7 +55968,7 @@
         <v>3</v>
       </c>
       <c r="K69" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="9" t="n">
         <v>1.4184</v>
@@ -55988,7 +55988,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>S. FRAILE DIAZ</t>
+          <t>L. KIEFER</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
@@ -55999,17 +55999,17 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H70" s="8" t="n">
@@ -56022,7 +56022,7 @@
         <v>3</v>
       </c>
       <c r="K70" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="9" t="n">
         <v>1.4184</v>
@@ -57392,7 +57392,7 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>M. COLOM ELOSÚA</t>
+          <t>E. SEVILLA ANTON</t>
         </is>
       </c>
       <c r="C96" s="8" t="n">
@@ -57403,12 +57403,12 @@
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="F96" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
         </is>
       </c>
       <c r="G96" s="8" t="inlineStr">
@@ -57446,7 +57446,7 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>E. SEVILLA ANTON</t>
+          <t>M. COLOM ELOSÚA</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
@@ -57457,12 +57457,12 @@
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
-        </is>
-      </c>
-      <c r="F97" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
@@ -57770,7 +57770,7 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>I. UGARTE PEREZ</t>
+          <t>M. VALDEANDE RUIZ</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
@@ -57824,7 +57824,7 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>M. VALDEANDE RUIZ</t>
+          <t>I. UGARTE PEREZ</t>
         </is>
       </c>
       <c r="C104" s="8" t="n">

--- a/fulls/full_mestre_lf2a_2026.xlsx
+++ b/fulls/full_mestre_lf2a_2026.xlsx
@@ -53936,18 +53936,18 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>N. PADROSA MONS</t>
+          <t>P. DE MIER ESPINA</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
         <v>8.1</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -53964,13 +53964,13 @@
         <v>0</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="8" t="n">
         <v>11</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L32" s="9" t="n">
         <v>1.6156</v>
@@ -53990,18 +53990,18 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>P. DE MIER ESPINA</t>
+          <t>N. PADROSA MONS</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
         <v>8.1</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
@@ -54018,13 +54018,13 @@
         <v>0</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="8" t="n">
         <v>11</v>
       </c>
       <c r="K33" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L33" s="9" t="n">
         <v>1.6156</v>
@@ -54206,41 +54206,41 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>A. BOBAR</t>
+          <t>S. LLANOS GASULLA</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
         <v>7</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H37" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>0</v>
+        <v>0.4286</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>0.7756999999999999</v>
@@ -54249,7 +54249,7 @@
         <v>0.9358</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>0.0597</v>
+        <v>0.1193</v>
       </c>
     </row>
     <row r="38">
@@ -54260,23 +54260,23 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>S. LLANOS GASULLA</t>
+          <t>A. BOBAR</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
         <v>7</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
@@ -54285,16 +54285,16 @@
         </is>
       </c>
       <c r="H38" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K38" s="10" t="n">
-        <v>0.4286</v>
+        <v>0</v>
       </c>
       <c r="L38" s="9" t="n">
         <v>0.7756999999999999</v>
@@ -54303,7 +54303,7 @@
         <v>0.9358</v>
       </c>
       <c r="N38" s="10" t="n">
-        <v>0.1193</v>
+        <v>0.0597</v>
       </c>
     </row>
     <row r="39">
@@ -54422,32 +54422,32 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>N. GOMEZ COBO</t>
+          <t>E. ABUBAKAR ARREY</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
         <v>6.3</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H41" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="8" t="n">
         <v>0</v>
@@ -54456,7 +54456,7 @@
         <v>4</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="9" t="n">
         <v>0.8185</v>
@@ -54465,7 +54465,7 @@
         <v>0.6863</v>
       </c>
       <c r="N41" s="10" t="n">
-        <v>0</v>
+        <v>0.07439999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -54530,18 +54530,18 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>E. ABUBAKAR ARREY</t>
+          <t>N. GOMEZ COBO</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
         <v>6.3</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
@@ -54551,11 +54551,11 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H43" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" s="8" t="n">
         <v>0</v>
@@ -54564,7 +54564,7 @@
         <v>4</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="9" t="n">
         <v>0.8185</v>
@@ -54573,7 +54573,7 @@
         <v>0.6863</v>
       </c>
       <c r="N43" s="10" t="n">
-        <v>0.07439999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -55124,18 +55124,18 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>A. BALLESTEROS MELGAR</t>
+          <t>C. DE LA OLIVA MARÍN</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -55145,14 +55145,14 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H54" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" s="8" t="n">
         <v>-1</v>
@@ -55178,18 +55178,18 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>C. DE LA OLIVA MARÍN</t>
+          <t>A. BALLESTEROS MELGAR</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -55199,14 +55199,14 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" s="8" t="n">
         <v>-1</v>
@@ -55502,18 +55502,18 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>G. JORGE GARCIA</t>
+          <t>A. DÉNES</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
         <v>4.3</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -55523,7 +55523,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H61" s="8" t="n">
@@ -55556,18 +55556,18 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>A. DÉNES</t>
+          <t>G. JORGE GARCIA</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
         <v>4.3</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
@@ -55577,7 +55577,7 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H62" s="8" t="n">
@@ -55610,14 +55610,14 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>M. LLORENTE RUIZ</t>
+          <t>C. MATO DE PRADA</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
         <v>4.3</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
@@ -55631,11 +55631,11 @@
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H63" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" s="8" t="n">
         <v>0</v>
@@ -55653,7 +55653,7 @@
         <v>0.5708</v>
       </c>
       <c r="N63" s="10" t="n">
-        <v>0.2049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -55664,14 +55664,14 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>C. MATO DE PRADA</t>
+          <t>M. LLORENTE RUIZ</t>
         </is>
       </c>
       <c r="C64" s="8" t="n">
         <v>4.3</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
@@ -55685,11 +55685,11 @@
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H64" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" s="8" t="n">
         <v>0</v>
@@ -55707,7 +55707,7 @@
         <v>0.5708</v>
       </c>
       <c r="N64" s="10" t="n">
-        <v>0</v>
+        <v>0.2049</v>
       </c>
     </row>
     <row r="65">
@@ -55934,28 +55934,28 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>S. FRAILE DIAZ</t>
+          <t>A. TORNE LABARTA</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F69" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H69" s="8" t="n">
@@ -55968,7 +55968,7 @@
         <v>3</v>
       </c>
       <c r="K69" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L69" s="9" t="n">
         <v>1.4184</v>
@@ -55988,7 +55988,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>L. KIEFER</t>
+          <t>S. FRAILE DIAZ</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
@@ -55999,17 +55999,17 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H70" s="8" t="n">
@@ -56022,7 +56022,7 @@
         <v>3</v>
       </c>
       <c r="K70" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" s="9" t="n">
         <v>1.4184</v>
@@ -56042,30 +56042,30 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>A. TORNE LABARTA</t>
+          <t>L. KIEFER</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H71" s="8" t="n">
         <v>0</v>
       </c>
@@ -56076,7 +56076,7 @@
         <v>3</v>
       </c>
       <c r="K71" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L71" s="9" t="n">
         <v>1.4184</v>
@@ -56150,50 +56150,50 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>N. IPO SERICHE-DOUGAN</t>
+          <t>D. MILIAUSKAITE</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H73" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K73" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>1.8895</v>
+        <v>2.2109</v>
       </c>
       <c r="M73" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="N73" s="10" t="n">
-        <v>0.1453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -56204,50 +56204,50 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>D. MILIAUSKAITE</t>
+          <t>N. IPO SERICHE-DOUGAN</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G74" s="8" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
       <c r="H74" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K74" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>2.2109</v>
+        <v>1.8895</v>
       </c>
       <c r="M74" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="N74" s="10" t="n">
-        <v>0</v>
+        <v>0.1453</v>
       </c>
     </row>
     <row r="75">
@@ -56906,32 +56906,32 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>N. CUNILL PEÑA</t>
+          <t>P. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G87" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H87" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" s="8" t="n">
         <v>0</v>
@@ -56940,7 +56940,7 @@
         <v>-3</v>
       </c>
       <c r="K87" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="9" t="n">
         <v>0.5</v>
@@ -56949,7 +56949,7 @@
         <v>1.6667</v>
       </c>
       <c r="N87" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="88">
@@ -56960,32 +56960,32 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>P. GARCIA GARCIA</t>
+          <t>N. CUNILL PEÑA</t>
         </is>
       </c>
       <c r="C88" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F88" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
       <c r="H88" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" s="8" t="n">
         <v>0</v>
@@ -56994,7 +56994,7 @@
         <v>-3</v>
       </c>
       <c r="K88" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="9" t="n">
         <v>0.5</v>
@@ -57003,7 +57003,7 @@
         <v>1.6667</v>
       </c>
       <c r="N88" s="10" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -57770,7 +57770,7 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>M. VALDEANDE RUIZ</t>
+          <t>I. UGARTE PEREZ</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
@@ -57824,7 +57824,7 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>I. UGARTE PEREZ</t>
+          <t>M. VALDEANDE RUIZ</t>
         </is>
       </c>
       <c r="C104" s="8" t="n">

--- a/fulls/full_mestre_lf2a_2026.xlsx
+++ b/fulls/full_mestre_lf2a_2026.xlsx
@@ -60157,50 +60157,50 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>M. GOMEZ HERNANDEZ</t>
+          <t>N. GOMEZ COBO</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>15</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>0/2</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H21" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>-8</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L21" s="11" t="n">
-        <v>0.4789</v>
+        <v>0.4723</v>
       </c>
       <c r="M21" s="11" t="n">
         <v>0.9055</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -60211,50 +60211,50 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>N. GOMEZ COBO</t>
+          <t>M. GOMEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>15</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>-8</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L22" s="11" t="n">
-        <v>0.4723</v>
+        <v>0.4789</v>
       </c>
       <c r="M22" s="11" t="n">
         <v>0.9055</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0</v>
+        <v>0.1277</v>
       </c>
     </row>
     <row r="23">
@@ -61237,18 +61237,18 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>N. PADROSA MONS</t>
+          <t>P. DE MIER ESPINA</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
         <v>8.1</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -61265,13 +61265,13 @@
         <v>0</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="8" t="n">
         <v>11</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L41" s="9" t="n">
         <v>1.6156</v>
@@ -61291,18 +61291,18 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>P. DE MIER ESPINA</t>
+          <t>N. PADROSA MONS</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
         <v>8.1</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -61319,13 +61319,13 @@
         <v>0</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="8" t="n">
         <v>11</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L42" s="9" t="n">
         <v>1.6156</v>
@@ -61615,23 +61615,23 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>S. LLANOS GASULLA</t>
+          <t>A. BOBAR</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
         <v>7</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
@@ -61640,16 +61640,16 @@
         </is>
       </c>
       <c r="H48" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J48" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>0.4286</v>
+        <v>0</v>
       </c>
       <c r="L48" s="9" t="n">
         <v>0.7756999999999999</v>
@@ -61658,7 +61658,7 @@
         <v>0.9358</v>
       </c>
       <c r="N48" s="10" t="n">
-        <v>0.1193</v>
+        <v>0.0597</v>
       </c>
     </row>
     <row r="49">
@@ -61669,41 +61669,41 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>A. BOBAR</t>
+          <t>S. LLANOS GASULLA</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
         <v>7</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H49" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J49" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>0</v>
+        <v>0.4286</v>
       </c>
       <c r="L49" s="9" t="n">
         <v>0.7756999999999999</v>
@@ -61712,7 +61712,7 @@
         <v>0.9358</v>
       </c>
       <c r="N49" s="10" t="n">
-        <v>0.0597</v>
+        <v>0.1193</v>
       </c>
     </row>
     <row r="50">
@@ -61885,7 +61885,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>M. OCURTO MENDES</t>
+          <t>L. PEREZ CASTRO</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
@@ -61896,24 +61896,24 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
       <c r="H53" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" s="8" t="n">
         <v>-5</v>
@@ -61928,7 +61928,7 @@
         <v>1.4523</v>
       </c>
       <c r="N53" s="10" t="n">
-        <v>0</v>
+        <v>0.1025</v>
       </c>
     </row>
     <row r="54">
@@ -61939,7 +61939,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>L. PEREZ CASTRO</t>
+          <t>M. OCURTO MENDES</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
@@ -61950,24 +61950,24 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G54" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H54" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="8" t="n">
         <v>-5</v>
@@ -61982,7 +61982,7 @@
         <v>1.4523</v>
       </c>
       <c r="N54" s="10" t="n">
-        <v>0.1025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -62533,23 +62533,23 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>N. CUNILL PEÑA</t>
+          <t>P. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
         <v>5.3</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
@@ -62567,7 +62567,7 @@
         <v>-1</v>
       </c>
       <c r="K65" s="10" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="L65" s="9" t="n">
         <v>1</v>
@@ -62587,23 +62587,23 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>P. GARCIA GARCIA</t>
+          <t>N. CUNILL PEÑA</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
         <v>5.3</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
@@ -62621,7 +62621,7 @@
         <v>-1</v>
       </c>
       <c r="K66" s="10" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="L66" s="9" t="n">
         <v>1</v>
@@ -62803,18 +62803,18 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>A. BALLESTEROS MELGAR</t>
+          <t>C. DE LA OLIVA MARÍN</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
@@ -62824,14 +62824,14 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H70" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I70" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" s="8" t="n">
         <v>-1</v>
@@ -62857,18 +62857,18 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>C. DE LA OLIVA MARÍN</t>
+          <t>A. BALLESTEROS MELGAR</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
@@ -62878,14 +62878,14 @@
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H71" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I71" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" s="8" t="n">
         <v>-1</v>
@@ -63127,14 +63127,14 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>C. MATO DE PRADA</t>
+          <t>M. LLORENTE RUIZ</t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
         <v>4.3</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
@@ -63148,11 +63148,11 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H76" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" s="8" t="n">
         <v>0</v>
@@ -63170,7 +63170,7 @@
         <v>0.5708</v>
       </c>
       <c r="N76" s="10" t="n">
-        <v>0</v>
+        <v>0.2049</v>
       </c>
     </row>
     <row r="77">
@@ -63181,14 +63181,14 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>M. LLORENTE RUIZ</t>
+          <t>C. MATO DE PRADA</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
         <v>4.3</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
@@ -63202,11 +63202,11 @@
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H77" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77" s="8" t="n">
         <v>0</v>
@@ -63224,7 +63224,7 @@
         <v>0.5708</v>
       </c>
       <c r="N77" s="10" t="n">
-        <v>0.2049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -64477,7 +64477,7 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>E. SEVILLA ANTON</t>
+          <t>M. COLOM ELOSÚA</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
@@ -64488,12 +64488,12 @@
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
-        </is>
-      </c>
-      <c r="F101" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
@@ -64531,7 +64531,7 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>M. COLOM ELOSÚA</t>
+          <t>E. SEVILLA ANTON</t>
         </is>
       </c>
       <c r="C102" s="8" t="n">
@@ -64542,12 +64542,12 @@
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F102" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr">
@@ -65125,7 +65125,7 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>I. BAUTISTA VILLAVERDE</t>
+          <t>O. BETANCOURT LABRADOR</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
@@ -65156,7 +65156,7 @@
         <v>0</v>
       </c>
       <c r="J113" s="8" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="K113" s="10" t="n">
         <v>0</v>
@@ -65165,7 +65165,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="9" t="n">
-        <v>0</v>
+        <v>2.2727</v>
       </c>
       <c r="N113" s="10" t="n">
         <v>0</v>
@@ -65179,7 +65179,7 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>O. BETANCOURT LABRADOR</t>
+          <t>I. BAUTISTA VILLAVERDE</t>
         </is>
       </c>
       <c r="C114" s="8" t="n">
@@ -65210,7 +65210,7 @@
         <v>0</v>
       </c>
       <c r="J114" s="8" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="K114" s="10" t="n">
         <v>0</v>
@@ -65219,7 +65219,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="9" t="n">
-        <v>2.2727</v>
+        <v>0</v>
       </c>
       <c r="N114" s="10" t="n">
         <v>0</v>

--- a/fulls/full_mestre_lf2a_2026.xlsx
+++ b/fulls/full_mestre_lf2a_2026.xlsx
@@ -60157,50 +60157,50 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>N. GOMEZ COBO</t>
+          <t>M. GOMEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>15</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
       <c r="H21" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>-8</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L21" s="11" t="n">
-        <v>0.4723</v>
+        <v>0.4789</v>
       </c>
       <c r="M21" s="11" t="n">
         <v>0.9055</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0</v>
+        <v>0.1277</v>
       </c>
     </row>
     <row r="22">
@@ -60211,50 +60211,50 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>M. GOMEZ HERNANDEZ</t>
+          <t>N. GOMEZ COBO</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>15</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>0/2</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>-8</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L22" s="11" t="n">
-        <v>0.4789</v>
+        <v>0.4723</v>
       </c>
       <c r="M22" s="11" t="n">
         <v>0.9055</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -61237,18 +61237,18 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>P. DE MIER ESPINA</t>
+          <t>N. PADROSA MONS</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
         <v>8.1</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -61265,13 +61265,13 @@
         <v>0</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="8" t="n">
         <v>11</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L41" s="9" t="n">
         <v>1.6156</v>
@@ -61291,18 +61291,18 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>N. PADROSA MONS</t>
+          <t>P. DE MIER ESPINA</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
         <v>8.1</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -61319,13 +61319,13 @@
         <v>0</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="8" t="n">
         <v>11</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L42" s="9" t="n">
         <v>1.6156</v>
@@ -62425,32 +62425,32 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>C. LOUREIRO CURRAS</t>
+          <t>L. TESSON</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H63" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" s="8" t="n">
         <v>0</v>
@@ -62459,7 +62459,7 @@
         <v>3</v>
       </c>
       <c r="K63" s="10" t="n">
-        <v>0.5833</v>
+        <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
         <v>1.0703</v>
@@ -62468,7 +62468,7 @@
         <v>0.9549</v>
       </c>
       <c r="N63" s="10" t="n">
-        <v>0.0765</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -62479,32 +62479,32 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>L. TESSON</t>
+          <t>C. LOUREIRO CURRAS</t>
         </is>
       </c>
       <c r="C64" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H64" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" s="8" t="n">
         <v>0</v>
@@ -62513,7 +62513,7 @@
         <v>3</v>
       </c>
       <c r="K64" s="10" t="n">
-        <v>0</v>
+        <v>0.5833</v>
       </c>
       <c r="L64" s="9" t="n">
         <v>1.0703</v>
@@ -62522,7 +62522,7 @@
         <v>0.9549</v>
       </c>
       <c r="N64" s="10" t="n">
-        <v>0</v>
+        <v>0.0765</v>
       </c>
     </row>
     <row r="65">
@@ -62533,23 +62533,23 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>P. GARCIA GARCIA</t>
+          <t>N. CUNILL PEÑA</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
         <v>5.3</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
@@ -62567,7 +62567,7 @@
         <v>-1</v>
       </c>
       <c r="K65" s="10" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="L65" s="9" t="n">
         <v>1</v>
@@ -62587,23 +62587,23 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>N. CUNILL PEÑA</t>
+          <t>P. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
         <v>5.3</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
@@ -62621,7 +62621,7 @@
         <v>-1</v>
       </c>
       <c r="K66" s="10" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="L66" s="9" t="n">
         <v>1</v>
@@ -63127,14 +63127,14 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>M. LLORENTE RUIZ</t>
+          <t>C. MATO DE PRADA</t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
         <v>4.3</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
@@ -63148,11 +63148,11 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H76" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76" s="8" t="n">
         <v>0</v>
@@ -63170,7 +63170,7 @@
         <v>0.5708</v>
       </c>
       <c r="N76" s="10" t="n">
-        <v>0.2049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -63181,14 +63181,14 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>C. MATO DE PRADA</t>
+          <t>M. LLORENTE RUIZ</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
         <v>4.3</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
@@ -63202,11 +63202,11 @@
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H77" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" s="8" t="n">
         <v>0</v>
@@ -63224,7 +63224,7 @@
         <v>0.5708</v>
       </c>
       <c r="N77" s="10" t="n">
-        <v>0</v>
+        <v>0.2049</v>
       </c>
     </row>
     <row r="78">
@@ -63289,50 +63289,50 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>N. IPO SERICHE-DOUGAN</t>
+          <t>D. MILIAUSKAITE</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H79" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K79" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>1.8895</v>
+        <v>2.2109</v>
       </c>
       <c r="M79" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="N79" s="10" t="n">
-        <v>0.1453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -63343,50 +63343,50 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>D. MILIAUSKAITE</t>
+          <t>N. IPO SERICHE-DOUGAN</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G80" s="8" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
       <c r="H80" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K80" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>2.2109</v>
+        <v>1.8895</v>
       </c>
       <c r="M80" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="N80" s="10" t="n">
-        <v>0</v>
+        <v>0.1453</v>
       </c>
     </row>
     <row r="81">
@@ -63397,50 +63397,50 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>C. LEAL FLORES</t>
+          <t>B. ARMENGOL VALL</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F81" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G81" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H81" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I81" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K81" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>1.0036</v>
+        <v>0.9291</v>
       </c>
       <c r="M81" s="9" t="n">
         <v>0.7991</v>
       </c>
       <c r="N81" s="10" t="n">
-        <v>0.0912</v>
+        <v>0.08450000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -63451,18 +63451,18 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>B. ARMENGOL VALL</t>
+          <t>C. LEAL FLORES</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
@@ -63479,22 +63479,22 @@
         <v>1</v>
       </c>
       <c r="I82" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K82" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>0.9291</v>
+        <v>1.0036</v>
       </c>
       <c r="M82" s="9" t="n">
         <v>0.7991</v>
       </c>
       <c r="N82" s="10" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.0912</v>
       </c>
     </row>
     <row r="83">
@@ -63991,7 +63991,7 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>M. REDONDO DE SANTA ANA</t>
+          <t>P. DIAZ MARTIN</t>
         </is>
       </c>
       <c r="C92" s="8" t="n">
@@ -64002,7 +64002,7 @@
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
@@ -64012,7 +64012,7 @@
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H92" s="8" t="n">
@@ -64025,7 +64025,7 @@
         <v>-2</v>
       </c>
       <c r="K92" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" s="9" t="n">
         <v>1.0309</v>
@@ -64045,7 +64045,7 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>P. DIAZ MARTIN</t>
+          <t>M. REDONDO DE SANTA ANA</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
@@ -64056,17 +64056,17 @@
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F93" s="8" t="inlineStr">
+      <c r="G93" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr">
-        <is>
-          <t>2/2</t>
         </is>
       </c>
       <c r="H93" s="8" t="n">
@@ -64079,7 +64079,7 @@
         <v>-2</v>
       </c>
       <c r="K93" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="9" t="n">
         <v>1.0309</v>
@@ -64477,7 +64477,7 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>M. COLOM ELOSÚA</t>
+          <t>E. SEVILLA ANTON</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
@@ -64488,12 +64488,12 @@
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="F101" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
@@ -64531,7 +64531,7 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>E. SEVILLA ANTON</t>
+          <t>M. COLOM ELOSÚA</t>
         </is>
       </c>
       <c r="C102" s="8" t="n">
@@ -64542,12 +64542,12 @@
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="F102" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
-        </is>
-      </c>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr">
@@ -64855,7 +64855,7 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>M. VALDEANDE RUIZ</t>
+          <t>I. UGARTE PEREZ</t>
         </is>
       </c>
       <c r="C108" s="8" t="n">
@@ -64909,7 +64909,7 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>I. UGARTE PEREZ</t>
+          <t>M. VALDEANDE RUIZ</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">

--- a/fulls/full_mestre_lf2a_2026.xlsx
+++ b/fulls/full_mestre_lf2a_2026.xlsx
@@ -60157,50 +60157,50 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>M. GOMEZ HERNANDEZ</t>
+          <t>N. GOMEZ COBO</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>15</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>0/2</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H21" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>-8</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L21" s="11" t="n">
-        <v>0.4789</v>
+        <v>0.4723</v>
       </c>
       <c r="M21" s="11" t="n">
         <v>0.9055</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.1277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -60211,50 +60211,50 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>N. GOMEZ COBO</t>
+          <t>M. GOMEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>15</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>-8</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L22" s="11" t="n">
-        <v>0.4723</v>
+        <v>0.4789</v>
       </c>
       <c r="M22" s="11" t="n">
         <v>0.9055</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0</v>
+        <v>0.1277</v>
       </c>
     </row>
     <row r="23">
@@ -60373,18 +60373,18 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>E. LARSEN</t>
+          <t>L. KIEFER</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>12.7</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -60394,26 +60394,26 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>15</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L25" s="11" t="n">
         <v>1.1516</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.3788</v>
+        <v>0.3719</v>
       </c>
       <c r="N25" s="6" t="n">
         <v>0</v>
@@ -60427,18 +60427,18 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>L. KIEFER</t>
+          <t>E. LARSEN</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>12.7</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -60448,26 +60448,26 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>15</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L26" s="11" t="n">
         <v>1.1516</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>0.3719</v>
+        <v>0.3788</v>
       </c>
       <c r="N26" s="6" t="n">
         <v>0</v>
@@ -61885,7 +61885,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>L. PEREZ CASTRO</t>
+          <t>M. OCURTO MENDES</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
@@ -61896,24 +61896,24 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H53" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" s="8" t="n">
         <v>-5</v>
@@ -61928,7 +61928,7 @@
         <v>1.4523</v>
       </c>
       <c r="N53" s="10" t="n">
-        <v>0.1025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -61939,7 +61939,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>M. OCURTO MENDES</t>
+          <t>L. PEREZ CASTRO</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
@@ -61950,24 +61950,24 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
       <c r="H54" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" s="8" t="n">
         <v>-5</v>
@@ -61982,7 +61982,7 @@
         <v>1.4523</v>
       </c>
       <c r="N54" s="10" t="n">
-        <v>0</v>
+        <v>0.1025</v>
       </c>
     </row>
     <row r="55">
@@ -61993,47 +61993,47 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>G. JORGE GARCIA</t>
+          <t>A. DÉNES</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
         <v>6.3</v>
       </c>
       <c r="D55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="H55" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="K55" s="10" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L55" s="9" t="n">
         <v>0.8621</v>
       </c>
       <c r="M55" s="9" t="n">
-        <v>1.1416</v>
+        <v>1.0152</v>
       </c>
       <c r="N55" s="10" t="n">
         <v>0</v>
@@ -62047,28 +62047,28 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>A. DÉNES</t>
+          <t>G. JORGE GARCIA</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
         <v>6.3</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H56" s="8" t="n">
@@ -62078,16 +62078,16 @@
         <v>0</v>
       </c>
       <c r="J56" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K56" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L56" s="9" t="n">
         <v>0.8621</v>
       </c>
       <c r="M56" s="9" t="n">
-        <v>1.0152</v>
+        <v>1.1416</v>
       </c>
       <c r="N56" s="10" t="n">
         <v>0</v>
@@ -62371,14 +62371,14 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>M. ANGULO QUINTANA</t>
+          <t>L. TESSON</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
@@ -62387,12 +62387,12 @@
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H62" s="8" t="n">
@@ -62425,14 +62425,14 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>L. TESSON</t>
+          <t>M. ANGULO QUINTANA</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
@@ -62441,12 +62441,12 @@
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H63" s="8" t="n">
@@ -62533,23 +62533,23 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>N. CUNILL PEÑA</t>
+          <t>P. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
         <v>5.3</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
@@ -62567,7 +62567,7 @@
         <v>-1</v>
       </c>
       <c r="K65" s="10" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="L65" s="9" t="n">
         <v>1</v>
@@ -62587,23 +62587,23 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>P. GARCIA GARCIA</t>
+          <t>N. CUNILL PEÑA</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
         <v>5.3</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
@@ -62621,7 +62621,7 @@
         <v>-1</v>
       </c>
       <c r="K66" s="10" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="L66" s="9" t="n">
         <v>1</v>
@@ -63019,7 +63019,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>H. DIAGNE EHEMBA</t>
+          <t>R. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
@@ -63040,14 +63040,14 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H74" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" s="8" t="n">
         <v>1</v>
@@ -63073,7 +63073,7 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>R. GARCIA GARCIA</t>
+          <t>H. DIAGNE EHEMBA</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
@@ -63094,14 +63094,14 @@
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H75" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I75" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" s="8" t="n">
         <v>1</v>
@@ -63127,14 +63127,14 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>C. MATO DE PRADA</t>
+          <t>M. LLORENTE RUIZ</t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
         <v>4.3</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
@@ -63148,11 +63148,11 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H76" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" s="8" t="n">
         <v>0</v>
@@ -63170,7 +63170,7 @@
         <v>0.5708</v>
       </c>
       <c r="N76" s="10" t="n">
-        <v>0</v>
+        <v>0.2049</v>
       </c>
     </row>
     <row r="77">
@@ -63181,14 +63181,14 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>M. LLORENTE RUIZ</t>
+          <t>C. MATO DE PRADA</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
         <v>4.3</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
@@ -63202,11 +63202,11 @@
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H77" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77" s="8" t="n">
         <v>0</v>
@@ -63224,7 +63224,7 @@
         <v>0.5708</v>
       </c>
       <c r="N77" s="10" t="n">
-        <v>0.2049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -63289,50 +63289,50 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>D. MILIAUSKAITE</t>
+          <t>N. IPO SERICHE-DOUGAN</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="G79" s="8" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
       <c r="H79" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K79" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>2.2109</v>
+        <v>1.8895</v>
       </c>
       <c r="M79" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="N79" s="10" t="n">
-        <v>0</v>
+        <v>0.1453</v>
       </c>
     </row>
     <row r="80">
@@ -63343,50 +63343,50 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>N. IPO SERICHE-DOUGAN</t>
+          <t>D. MILIAUSKAITE</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F80" s="8" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H80" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" s="8" t="n">
         <v>10</v>
       </c>
       <c r="K80" s="10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>1.8895</v>
+        <v>2.2109</v>
       </c>
       <c r="M80" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="N80" s="10" t="n">
-        <v>0.1453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -64477,7 +64477,7 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>E. SEVILLA ANTON</t>
+          <t>M. COLOM ELOSÚA</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
@@ -64488,12 +64488,12 @@
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
-        </is>
-      </c>
-      <c r="F101" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
@@ -64531,7 +64531,7 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>M. COLOM ELOSÚA</t>
+          <t>E. SEVILLA ANTON</t>
         </is>
       </c>
       <c r="C102" s="8" t="n">
@@ -64542,12 +64542,12 @@
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F102" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr">

--- a/fulls/full_mestre_lf2a_2026.xlsx
+++ b/fulls/full_mestre_lf2a_2026.xlsx
@@ -60157,50 +60157,50 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>N. GOMEZ COBO</t>
+          <t>M. GOMEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>15</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
       <c r="H21" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>-8</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L21" s="11" t="n">
-        <v>0.4723</v>
+        <v>0.4789</v>
       </c>
       <c r="M21" s="11" t="n">
         <v>0.9055</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0</v>
+        <v>0.1277</v>
       </c>
     </row>
     <row r="22">
@@ -60211,50 +60211,50 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>M. GOMEZ HERNANDEZ</t>
+          <t>N. GOMEZ COBO</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>15</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>0/2</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>-8</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L22" s="11" t="n">
-        <v>0.4789</v>
+        <v>0.4723</v>
       </c>
       <c r="M22" s="11" t="n">
         <v>0.9055</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -61237,18 +61237,18 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>N. PADROSA MONS</t>
+          <t>P. DE MIER ESPINA</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
         <v>8.1</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -61265,13 +61265,13 @@
         <v>0</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="8" t="n">
         <v>11</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L41" s="9" t="n">
         <v>1.6156</v>
@@ -61291,18 +61291,18 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>P. DE MIER ESPINA</t>
+          <t>N. PADROSA MONS</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
         <v>8.1</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -61319,13 +61319,13 @@
         <v>0</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="8" t="n">
         <v>11</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L42" s="9" t="n">
         <v>1.6156</v>
@@ -61615,41 +61615,41 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>A. BOBAR</t>
+          <t>S. LLANOS GASULLA</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
         <v>7</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="G48" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H48" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J48" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>0</v>
+        <v>0.4286</v>
       </c>
       <c r="L48" s="9" t="n">
         <v>0.7756999999999999</v>
@@ -61658,7 +61658,7 @@
         <v>0.9358</v>
       </c>
       <c r="N48" s="10" t="n">
-        <v>0.0597</v>
+        <v>0.1193</v>
       </c>
     </row>
     <row r="49">
@@ -61669,23 +61669,23 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>S. LLANOS GASULLA</t>
+          <t>A. BOBAR</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
         <v>7</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
@@ -61694,16 +61694,16 @@
         </is>
       </c>
       <c r="H49" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J49" s="8" t="n">
         <v>-1</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>0.4286</v>
+        <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
         <v>0.7756999999999999</v>
@@ -61712,7 +61712,7 @@
         <v>0.9358</v>
       </c>
       <c r="N49" s="10" t="n">
-        <v>0.1193</v>
+        <v>0.0597</v>
       </c>
     </row>
     <row r="50">
@@ -61993,28 +61993,28 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>A. DÉNES</t>
+          <t>G. JORGE GARCIA</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
         <v>6.3</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
+          <t>1/3</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
@@ -62024,16 +62024,16 @@
         <v>0</v>
       </c>
       <c r="J55" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K55" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L55" s="9" t="n">
         <v>0.8621</v>
       </c>
       <c r="M55" s="9" t="n">
-        <v>1.0152</v>
+        <v>1.1416</v>
       </c>
       <c r="N55" s="10" t="n">
         <v>0</v>
@@ -62047,47 +62047,47 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>G. JORGE GARCIA</t>
+          <t>A. DÉNES</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
         <v>6.3</v>
       </c>
       <c r="D56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G56" s="8" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="H56" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="K56" s="10" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
         <v>0.8621</v>
       </c>
       <c r="M56" s="9" t="n">
-        <v>1.1416</v>
+        <v>1.0152</v>
       </c>
       <c r="N56" s="10" t="n">
         <v>0</v>
@@ -62371,14 +62371,14 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>L. TESSON</t>
+          <t>M. ANGULO QUINTANA</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
@@ -62387,12 +62387,12 @@
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H62" s="8" t="n">
@@ -62425,14 +62425,14 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>M. ANGULO QUINTANA</t>
+          <t>L. TESSON</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
@@ -62441,12 +62441,12 @@
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H63" s="8" t="n">
@@ -63019,7 +63019,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>R. GARCIA GARCIA</t>
+          <t>H. DIAGNE EHEMBA</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
@@ -63040,14 +63040,14 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H74" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" s="8" t="n">
         <v>1</v>
@@ -63073,7 +63073,7 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>H. DIAGNE EHEMBA</t>
+          <t>R. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
@@ -63094,14 +63094,14 @@
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H75" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I75" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" s="8" t="n">
         <v>1</v>
@@ -63397,18 +63397,18 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>B. ARMENGOL VALL</t>
+          <t>C. LEAL FLORES</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
@@ -63425,22 +63425,22 @@
         <v>1</v>
       </c>
       <c r="I81" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K81" s="10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>0.9291</v>
+        <v>1.0036</v>
       </c>
       <c r="M81" s="9" t="n">
         <v>0.7991</v>
       </c>
       <c r="N81" s="10" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.0912</v>
       </c>
     </row>
     <row r="82">
@@ -63451,50 +63451,50 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>C. LEAL FLORES</t>
+          <t>B. ARMENGOL VALL</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="F82" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="G82" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
       <c r="H82" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I82" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K82" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>1.0036</v>
+        <v>0.9291</v>
       </c>
       <c r="M82" s="9" t="n">
         <v>0.7991</v>
       </c>
       <c r="N82" s="10" t="n">
-        <v>0.0912</v>
+        <v>0.08450000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -64477,7 +64477,7 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>M. COLOM ELOSÚA</t>
+          <t>E. SEVILLA ANTON</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
@@ -64488,12 +64488,12 @@
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
           <t>0/0</t>
-        </is>
-      </c>
-      <c r="F101" s="8" t="inlineStr">
-        <is>
-          <t>0/1</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
@@ -64531,7 +64531,7 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>E. SEVILLA ANTON</t>
+          <t>M. COLOM ELOSÚA</t>
         </is>
       </c>
       <c r="C102" s="8" t="n">
@@ -64542,12 +64542,12 @@
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="F102" s="8" t="inlineStr">
+        <is>
           <t>0/1</t>
-        </is>
-      </c>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>0/0</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr">
@@ -65125,7 +65125,7 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>O. BETANCOURT LABRADOR</t>
+          <t>I. BAUTISTA VILLAVERDE</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
@@ -65156,7 +65156,7 @@
         <v>0</v>
       </c>
       <c r="J113" s="8" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="K113" s="10" t="n">
         <v>0</v>
@@ -65165,7 +65165,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="9" t="n">
-        <v>2.2727</v>
+        <v>0</v>
       </c>
       <c r="N113" s="10" t="n">
         <v>0</v>
@@ -65179,7 +65179,7 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>I. BAUTISTA VILLAVERDE</t>
+          <t>O. BETANCOURT LABRADOR</t>
         </is>
       </c>
       <c r="C114" s="8" t="n">
@@ -65210,7 +65210,7 @@
         <v>0</v>
       </c>
       <c r="J114" s="8" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="K114" s="10" t="n">
         <v>0</v>
@@ -65219,7 +65219,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="9" t="n">
-        <v>0</v>
+        <v>2.2727</v>
       </c>
       <c r="N114" s="10" t="n">
         <v>0</v>
